--- a/artfynd/A 13309-2022 artfynd.xlsx
+++ b/artfynd/A 13309-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129109529</v>
       </c>
       <c r="B2" t="n">
-        <v>92321</v>
+        <v>92326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129109566</v>
       </c>
       <c r="B3" t="n">
-        <v>91975</v>
+        <v>91978</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 13309-2022 artfynd.xlsx
+++ b/artfynd/A 13309-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129109529</v>
       </c>
       <c r="B2" t="n">
-        <v>92326</v>
+        <v>92329</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129109566</v>
       </c>
       <c r="B3" t="n">
-        <v>91978</v>
+        <v>91981</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 13309-2022 artfynd.xlsx
+++ b/artfynd/A 13309-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129109529</v>
       </c>
       <c r="B2" t="n">
-        <v>92329</v>
+        <v>92336</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129109566</v>
       </c>
       <c r="B3" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 13309-2022 artfynd.xlsx
+++ b/artfynd/A 13309-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129109529</v>
       </c>
       <c r="B2" t="n">
-        <v>92336</v>
+        <v>92343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129109566</v>
       </c>
       <c r="B3" t="n">
-        <v>91988</v>
+        <v>91995</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 13309-2022 artfynd.xlsx
+++ b/artfynd/A 13309-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129109529</v>
       </c>
       <c r="B2" t="n">
-        <v>92343</v>
+        <v>92345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129109566</v>
       </c>
       <c r="B3" t="n">
-        <v>91995</v>
+        <v>91997</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 13309-2022 artfynd.xlsx
+++ b/artfynd/A 13309-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129109529</v>
       </c>
       <c r="B2" t="n">
-        <v>92345</v>
+        <v>92359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129109566</v>
       </c>
       <c r="B3" t="n">
-        <v>91997</v>
+        <v>91992</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,12 +796,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>

--- a/artfynd/A 13309-2022 artfynd.xlsx
+++ b/artfynd/A 13309-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129109529</v>
       </c>
       <c r="B2" t="n">
-        <v>92359</v>
+        <v>92360</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129109566</v>
       </c>
       <c r="B3" t="n">
-        <v>91992</v>
+        <v>91993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 13309-2022 artfynd.xlsx
+++ b/artfynd/A 13309-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129109529</v>
       </c>
       <c r="B2" t="n">
-        <v>92360</v>
+        <v>92363</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129109566</v>
       </c>
       <c r="B3" t="n">
-        <v>91993</v>
+        <v>91996</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 13309-2022 artfynd.xlsx
+++ b/artfynd/A 13309-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129109529</v>
       </c>
       <c r="B2" t="n">
-        <v>92363</v>
+        <v>92365</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129109566</v>
       </c>
       <c r="B3" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 13309-2022 artfynd.xlsx
+++ b/artfynd/A 13309-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129109529</v>
       </c>
       <c r="B2" t="n">
-        <v>92365</v>
+        <v>92369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129109566</v>
       </c>
       <c r="B3" t="n">
-        <v>91998</v>
+        <v>92002</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 13309-2022 artfynd.xlsx
+++ b/artfynd/A 13309-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129109529</v>
       </c>
       <c r="B2" t="n">
-        <v>92369</v>
+        <v>92370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129109566</v>
       </c>
       <c r="B3" t="n">
-        <v>92002</v>
+        <v>92003</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 13309-2022 artfynd.xlsx
+++ b/artfynd/A 13309-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129109529</v>
       </c>
       <c r="B2" t="n">
-        <v>92370</v>
+        <v>92373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129109566</v>
       </c>
       <c r="B3" t="n">
-        <v>92003</v>
+        <v>92006</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 13309-2022 artfynd.xlsx
+++ b/artfynd/A 13309-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129109529</v>
+        <v>129109566</v>
       </c>
       <c r="B2" t="n">
-        <v>92373</v>
+        <v>92369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2014</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628961</v>
+        <v>628973</v>
       </c>
       <c r="R2" t="n">
-        <v>7017960</v>
+        <v>7017933</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129109566</v>
+        <v>129109529</v>
       </c>
       <c r="B3" t="n">
-        <v>92006</v>
+        <v>92732</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>2014</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628973</v>
+        <v>628961</v>
       </c>
       <c r="R3" t="n">
-        <v>7017933</v>
+        <v>7017960</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 13309-2022 artfynd.xlsx
+++ b/artfynd/A 13309-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129109566</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,8 +884,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129109529</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>